--- a/Shared/XLS/Costume.xlsx
+++ b/Shared/XLS/Costume.xlsx
@@ -107,44 +107,46 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>!CostumeType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!WeaponType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>요술봉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DualBlades</t>
+  </si>
+  <si>
+    <t>BodySet_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsDefault</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SetAddress</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponSet_DualBlades_101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>BodySet_Default</t>
-  </si>
-  <si>
-    <t>!CostumeType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!WeaponType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>요술봉</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponSet_DualBlades_101</t>
-  </si>
-  <si>
-    <t>DualBlades</t>
-  </si>
-  <si>
-    <t>BodySet_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!bool</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsDefault</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SetAddress</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -628,7 +630,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -729,13 +731,13 @@
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>13</v>
@@ -759,16 +761,16 @@
         <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>12</v>
@@ -789,7 +791,7 @@
         <v>6</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I4" s="1" t="b">
         <v>1</v>
@@ -807,7 +809,7 @@
         <v>6</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>18</v>
@@ -821,16 +823,16 @@
         <v>2001</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>5</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>18</v>

--- a/Shared/XLS/Costume.xlsx
+++ b/Shared/XLS/Costume.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
   <si>
     <t>!Table</t>
   </si>
@@ -115,38 +115,69 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>요술봉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DualBlades</t>
+  </si>
+  <si>
+    <t>BodySet_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SetAddress</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponSet_DualBlades_101</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BodySet_Default</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Acquisition</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>상점 구매</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>히드라 처치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>WeaponType</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>요술봉</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DualBlades</t>
-  </si>
-  <si>
-    <t>BodySet_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!bool</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>CostumeType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ItemGradeType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Grade</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mythic</t>
   </si>
   <si>
     <t>IsDefault</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SetAddress</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponSet_DualBlades_101</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>BodySet_Default</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -689,23 +720,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="2" width="10.25" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="6.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="26.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -713,7 +746,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="7" t="s">
         <v>1</v>
@@ -728,25 +761,31 @@
         <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="8" t="s">
         <v>2</v>
@@ -761,25 +800,31 @@
         <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="1">
         <v>1001</v>
@@ -787,17 +832,17 @@
       <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="H4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="1" t="b">
+      <c r="J4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="1">
         <v>1002</v>
@@ -805,46 +850,58 @@
       <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="J5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="1">
+      <c r="M5" s="1">
         <v>3000</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>2001</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="J6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="1">
+      <c r="M6" s="1">
         <v>2500</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Costume.xlsx
+++ b/Shared/XLS/Costume.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>!Table</t>
   </si>
@@ -178,6 +178,14 @@
   </si>
   <si>
     <t>IsDefault</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponCostume_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BodyCostume_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -724,9 +732,10 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
-    <col min="2" max="2" width="10.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.875" style="1" bestFit="1" customWidth="1"/>
@@ -827,7 +836,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="1">
-        <v>1001</v>
+        <v>1040100001</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>16</v>
@@ -845,11 +854,14 @@
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="1">
-        <v>1002</v>
+        <v>1040100002</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="E5" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>36</v>
       </c>
@@ -871,10 +883,13 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
-        <v>2001</v>
+        <v>1040100003</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>36</v>

--- a/Shared/XLS/Costume.xlsx
+++ b/Shared/XLS/Costume.xlsx
@@ -119,9 +119,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>DualBlades</t>
-  </si>
-  <si>
     <t>BodySet_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -134,10 +131,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>WeaponSet_DualBlades_101</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>BodySet_Default</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -186,6 +179,14 @@
   </si>
   <si>
     <t>BodyCostume_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreatSword</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon_GreatSword_01</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -770,22 +771,22 @@
         <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>13</v>
@@ -809,10 +810,10 @@
         <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>19</v>
@@ -824,7 +825,7 @@
         <v>14</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>12</v>
@@ -845,7 +846,7 @@
         <v>6</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K4" s="1" t="b">
         <v>1</v>
@@ -860,19 +861,19 @@
         <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>18</v>
@@ -889,22 +890,22 @@
         <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>5</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>18</v>
